--- a/output/ValueSet-botswana-amr-organism-vs.xlsx
+++ b/output/ValueSet-botswana-amr-organism-vs.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-organism-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-organism-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,7 +121,7 @@
     <t>All codes</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/CodeSystem/botswana-amr-local-organism-cs</t>
+    <t>http://bw.health.gov/fhir/amr/CodeSystem/botswana-amr-local-organism-cs</t>
   </si>
 </sst>
 </file>
